--- a/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -752,51 +752,51 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
         <v>22</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>8.31</v>
+        <v>7.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -806,51 +806,51 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="I7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J7" t="n">
+        <v>23</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9</v>
+      </c>
+      <c r="M7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
-        <v>39</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" t="n">
-        <v>27</v>
-      </c>
       <c r="N7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>8.33</v>
+        <v>6.03</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8">
@@ -864,47 +864,47 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="J8" t="n">
+        <v>18</v>
+      </c>
+      <c r="K8" t="n">
         <v>9</v>
       </c>
-      <c r="K8" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="N8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="O8" t="n">
-        <v>6.55</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="9">
@@ -918,47 +918,47 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J9" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
         <v>21</v>
       </c>
-      <c r="M9" t="n">
-        <v>30</v>
-      </c>
       <c r="N9" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="O9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.31</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="10">
@@ -972,47 +972,47 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N10" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>8.33</v>
       </c>
       <c r="P10" t="n">
-        <v>2.52</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -1022,51 +1022,51 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="O11" t="n">
-        <v>6.08</v>
+        <v>6.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="12">
@@ -1076,51 +1076,51 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>7</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>8</v>
-      </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="N12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="O12" t="n">
-        <v>5.14</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1130,51 +1130,51 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>7</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
         <v>15</v>
       </c>
       <c r="N13" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>5.24</v>
+        <v>3.17</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="14">
@@ -1184,51 +1184,51 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J14" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>5.55</v>
+        <v>6.08</v>
       </c>
       <c r="P14" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
@@ -1238,33 +1238,33 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
         <v>7</v>
@@ -1273,16 +1273,16 @@
         <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="O15" t="n">
-        <v>4.66</v>
+        <v>5.55</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="16">
@@ -1292,51 +1292,51 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
+        <v>23</v>
+      </c>
+      <c r="I16" t="n">
         <v>18</v>
       </c>
-      <c r="I16" t="n">
-        <v>13</v>
-      </c>
       <c r="J16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
         <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N16" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="O16" t="n">
-        <v>6.67</v>
+        <v>4.66</v>
       </c>
       <c r="P16" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
@@ -1346,51 +1346,51 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O17" t="n">
-        <v>3.63</v>
+        <v>6.67</v>
       </c>
       <c r="P17" t="n">
-        <v>1.65</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="18">
@@ -1400,51 +1400,51 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
+        <v>23</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="n">
         <v>8</v>
       </c>
-      <c r="G18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H18" t="n">
-        <v>21</v>
-      </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="N18" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O18" t="n">
-        <v>6.55</v>
+        <v>3.63</v>
       </c>
       <c r="P18" t="n">
-        <v>0.92</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="19">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1573,22 +1573,22 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I21" t="n">
+        <v>21</v>
+      </c>
+      <c r="J21" t="n">
         <v>15</v>
-      </c>
-      <c r="J21" t="n">
-        <v>12</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
@@ -1597,16 +1597,16 @@
         <v>5</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="P21" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="22">
@@ -3198,16 +3198,16 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>22.08333333333333</v>
+        <v>22.20833333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>13.09674855431818</v>
+        <v>12.98273539897183</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
         <v>19</v>
@@ -3229,10 +3229,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>3.583333333333333</v>
+        <v>3.645833333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>2.886751345948129</v>
+        <v>2.928143579590153</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3260,25 +3260,25 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>40.79166666666666</v>
+        <v>41.95833333333334</v>
       </c>
       <c r="D4" t="n">
-        <v>16.7750553581651</v>
+        <v>18.07661982775439</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>29.75</v>
       </c>
       <c r="G4" t="n">
         <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>49.25</v>
+        <v>52.25</v>
       </c>
       <c r="I4" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
@@ -3291,10 +3291,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>11.85416666666667</v>
+        <v>11.79166666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>6.219357507123902</v>
+        <v>6.129657007978587</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3306,7 +3306,7 @@
         <v>11.5</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I5" t="n">
         <v>25</v>
@@ -3322,16 +3322,16 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>25.1875</v>
+        <v>25.8125</v>
       </c>
       <c r="D6" t="n">
-        <v>12.67373939343736</v>
+        <v>13.33633055851412</v>
       </c>
       <c r="E6" t="n">
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="G6" t="n">
         <v>22</v>
@@ -3340,7 +3340,7 @@
         <v>35</v>
       </c>
       <c r="I6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -3353,10 +3353,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>13.89583333333333</v>
+        <v>14.22916666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>7.279348764808312</v>
+        <v>7.492519910546056</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -3365,10 +3365,10 @@
         <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
         <v>34</v>
@@ -3384,10 +3384,10 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>15.60416666666667</v>
+        <v>16.14583333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>6.357236062520404</v>
+        <v>6.964926061018953</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
@@ -3399,7 +3399,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>18.5</v>
+        <v>20.25</v>
       </c>
       <c r="I8" t="n">
         <v>33</v>
@@ -3415,10 +3415,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>15.27083333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>7.819778524370927</v>
+        <v>7.911046904207267</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H9" t="n">
-        <v>19.25</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
         <v>39</v>
@@ -3446,10 +3446,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>4.875</v>
+        <v>5.020833333333333</v>
       </c>
       <c r="D10" t="n">
-        <v>3.16648002436157</v>
+        <v>3.322967037013461</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
         <v>13</v>
@@ -3477,10 +3477,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>6.770833333333333</v>
+        <v>6.875</v>
       </c>
       <c r="D11" t="n">
-        <v>3.979947520948429</v>
+        <v>4.045617539584748</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -3508,25 +3508,25 @@
         <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>17.20833333333333</v>
+        <v>17.79166666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>6.961775065077698</v>
+        <v>7.573633809342394</v>
       </c>
       <c r="E12" t="n">
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>13.75</v>
       </c>
       <c r="G12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="I12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -3539,10 +3539,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>45.29166666666666</v>
+        <v>45.20833333333334</v>
       </c>
       <c r="D13" t="n">
-        <v>9.057636564901685</v>
+        <v>8.939413882765239</v>
       </c>
       <c r="E13" t="n">
         <v>28</v>
@@ -3554,7 +3554,7 @@
         <v>45.5</v>
       </c>
       <c r="H13" t="n">
-        <v>52.25</v>
+        <v>52</v>
       </c>
       <c r="I13" t="n">
         <v>62</v>
@@ -3570,10 +3570,10 @@
         <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>4.165416666666666</v>
+        <v>4.265833333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>2.23195359359724</v>
+        <v>2.328106557235723</v>
       </c>
       <c r="E14" t="n">
         <v>1.12</v>
@@ -3585,7 +3585,7 @@
         <v>3.735</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6325</v>
+        <v>6.0425</v>
       </c>
       <c r="I14" t="n">
         <v>8.640000000000001</v>
@@ -3601,10 +3601,10 @@
         <v>48</v>
       </c>
       <c r="C15" t="n">
-        <v>1.184791666666667</v>
+        <v>1.181458333333333</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5518633410212356</v>
+        <v>0.5353344136118685</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3613,13 +3613,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.125</v>
+        <v>1.13</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5375</v>
+        <v>1.525</v>
       </c>
       <c r="I15" t="n">
-        <v>2.73</v>
+        <v>2.52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
@@ -426,104 +426,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Attempts At Goal</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Attempts At Goal Conv. Rate (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Attempts At Goal</t>
+          <t>Attempts Inside the Penalty Area</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Attempts At Goal Conv. Rate (%)</t>
+          <t>Attempts On Target</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Attempts Inside the Penalty Area</t>
+          <t>Attempts Outside the Penalty Area</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Attempts On Target</t>
+          <t>Corners</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Attempts Outside the Penalty Area</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Corners</t>
+          <t>Headed Attempts at Goal</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Off-Target Attempts</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Headed Attempts at Goal</t>
+          <t>Possession Control (%)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Off-Target Attempts</t>
+          <t>xG</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Possession Control (%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>xG</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>xG Efficiency</t>
         </is>
@@ -532,2593 +520,2209 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>36</v>
       </c>
       <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="n">
-        <v>73</v>
-      </c>
-      <c r="F2" t="n">
-        <v>18</v>
-      </c>
-      <c r="G2" t="n">
-        <v>43</v>
-      </c>
-      <c r="H2" t="n">
-        <v>34</v>
-      </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="M2" t="n">
-        <v>26</v>
+        <v>3.99</v>
       </c>
       <c r="N2" t="n">
-        <v>51</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="M3" t="n">
-        <v>26</v>
+        <v>6.55</v>
       </c>
       <c r="N3" t="n">
-        <v>56</v>
-      </c>
-      <c r="O3" t="n">
-        <v>8.640000000000001</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="n">
-        <v>46</v>
-      </c>
-      <c r="F4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
         <v>35</v>
       </c>
-      <c r="H4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L4" t="n">
-        <v>14</v>
-      </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>1.99</v>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+      <c r="C5" t="n">
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>3.63</v>
       </c>
       <c r="N5" t="n">
-        <v>47</v>
-      </c>
-      <c r="O5" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>92</v>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
-        <v>68</v>
-      </c>
-      <c r="F6" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
         <v>38</v>
       </c>
-      <c r="H6" t="n">
-        <v>22</v>
-      </c>
-      <c r="I6" t="n">
-        <v>30</v>
-      </c>
-      <c r="J6" t="n">
-        <v>22</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10</v>
-      </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>49</v>
-      </c>
-      <c r="O6" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>37</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>2.04</v>
       </c>
       <c r="N7" t="n">
-        <v>52</v>
-      </c>
-      <c r="O7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>22</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
         <v>10</v>
       </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>26</v>
-      </c>
-      <c r="I8" t="n">
-        <v>32</v>
-      </c>
-      <c r="J8" t="n">
-        <v>18</v>
-      </c>
       <c r="K8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>38</v>
+        <v>8.31</v>
       </c>
       <c r="N8" t="n">
-        <v>51</v>
-      </c>
-      <c r="O8" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
         <v>7</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" t="n">
-        <v>15</v>
-      </c>
       <c r="G9" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="M9" t="n">
-        <v>21</v>
+        <v>2.04</v>
       </c>
       <c r="N9" t="n">
-        <v>52</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8.31</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
+        <v>71</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="M10" t="n">
-        <v>27</v>
+        <v>8.33</v>
       </c>
       <c r="N10" t="n">
-        <v>49</v>
-      </c>
-      <c r="O10" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="P10" t="n">
         <v>1.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>59</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>35</v>
       </c>
       <c r="F11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
         <v>23</v>
       </c>
-      <c r="G11" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" t="n">
-        <v>15</v>
-      </c>
-      <c r="I11" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" t="n">
-        <v>8</v>
-      </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>4.55</v>
       </c>
       <c r="N11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.22</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" t="n">
         <v>10</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" t="n">
-        <v>74</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11</v>
-      </c>
       <c r="G12" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="H12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>3.71</v>
       </c>
       <c r="N12" t="n">
-        <v>58</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8.470000000000001</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
       </c>
       <c r="D13" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13</v>
+      </c>
+      <c r="H13" t="n">
         <v>7</v>
       </c>
-      <c r="E13" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G13" t="n">
-        <v>16</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>2.24</v>
       </c>
       <c r="N13" t="n">
-        <v>42</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>29</v>
       </c>
       <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" t="n">
-        <v>50</v>
-      </c>
-      <c r="F14" t="n">
-        <v>16</v>
-      </c>
       <c r="G14" t="n">
+        <v>15</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18</v>
+      </c>
+      <c r="L14" t="n">
         <v>32</v>
       </c>
-      <c r="H14" t="n">
-        <v>16</v>
-      </c>
-      <c r="I14" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10</v>
-      </c>
       <c r="M14" t="n">
-        <v>25</v>
+        <v>1.7</v>
       </c>
       <c r="N14" t="n">
-        <v>45</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.32</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="n">
         <v>12</v>
       </c>
-      <c r="G15" t="n">
-        <v>35</v>
-      </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>19</v>
+        <v>2.44</v>
       </c>
       <c r="N15" t="n">
-        <v>55</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.26</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>30</v>
+      </c>
+      <c r="F16" t="n">
         <v>14</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E16" t="n">
-        <v>48</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>15</v>
       </c>
-      <c r="G16" t="n">
-        <v>30</v>
-      </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="M16" t="n">
-        <v>18</v>
+        <v>5.5</v>
       </c>
       <c r="N16" t="n">
-        <v>43</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.5</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>53</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>17</v>
+        <v>5.88</v>
       </c>
       <c r="N17" t="n">
-        <v>55</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F18" t="n">
+        <v>13</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" t="n">
+        <v>18</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
         <v>23</v>
       </c>
-      <c r="G18" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" t="n">
-        <v>11</v>
-      </c>
-      <c r="J18" t="n">
-        <v>10</v>
-      </c>
-      <c r="K18" t="n">
-        <v>6</v>
-      </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="M18" t="n">
-        <v>14</v>
+        <v>3.76</v>
       </c>
       <c r="N18" t="n">
-        <v>44</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C19" t="n">
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.68</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>73</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>14</v>
+        <v>7.86</v>
       </c>
       <c r="N20" t="n">
-        <v>58</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>74</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H21" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="M21" t="n">
-        <v>14</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
       </c>
       <c r="D22" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>11</v>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
-        <v>41</v>
-      </c>
-      <c r="F22" t="n">
-        <v>12</v>
-      </c>
       <c r="G22" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="M22" t="n">
-        <v>25</v>
+        <v>2.07</v>
       </c>
       <c r="N22" t="n">
-        <v>37</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.35</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>31</v>
       </c>
       <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="n">
-        <v>24</v>
-      </c>
-      <c r="F23" t="n">
-        <v>21</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11</v>
-      </c>
-      <c r="H23" t="n">
-        <v>11</v>
-      </c>
-      <c r="I23" t="n">
-        <v>13</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="M23" t="n">
-        <v>9</v>
+        <v>1.62</v>
       </c>
       <c r="N23" t="n">
-        <v>49</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.23</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>37</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" t="n">
         <v>11</v>
       </c>
-      <c r="G24" t="n">
-        <v>30</v>
-      </c>
       <c r="H24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" t="n">
         <v>15</v>
       </c>
-      <c r="J24" t="n">
-        <v>26</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5</v>
-      </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>17</v>
+        <v>4.57</v>
       </c>
       <c r="N24" t="n">
-        <v>45</v>
-      </c>
-      <c r="O24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>21</v>
       </c>
       <c r="D25" t="n">
         <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K25" t="n">
         <v>13</v>
       </c>
-      <c r="I25" t="n">
-        <v>18</v>
-      </c>
-      <c r="J25" t="n">
-        <v>18</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5</v>
-      </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>23</v>
+        <v>2.11</v>
       </c>
       <c r="N25" t="n">
-        <v>47</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.33</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>19</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C26" t="n">
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L26" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>26</v>
+        <v>3.17</v>
       </c>
       <c r="N26" t="n">
-        <v>62</v>
-      </c>
-      <c r="O26" t="n">
-        <v>6.58</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.76</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H27" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="M27" t="n">
-        <v>23</v>
+        <v>1.87</v>
       </c>
       <c r="N27" t="n">
-        <v>56</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.88</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
+        <v>11</v>
+      </c>
+      <c r="G28" t="n">
+        <v>11</v>
+      </c>
+      <c r="H28" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9</v>
+      </c>
+      <c r="K28" t="n">
         <v>13</v>
       </c>
-      <c r="G28" t="n">
-        <v>19</v>
-      </c>
-      <c r="H28" t="n">
-        <v>15</v>
-      </c>
-      <c r="I28" t="n">
-        <v>12</v>
-      </c>
-      <c r="J28" t="n">
-        <v>10</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4</v>
-      </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="M28" t="n">
-        <v>8</v>
+        <v>3.38</v>
       </c>
       <c r="N28" t="n">
-        <v>42</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.62</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C29" t="n">
+        <v>50</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I29" t="n">
         <v>8</v>
       </c>
-      <c r="G29" t="n">
-        <v>26</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="I29" t="n">
-        <v>11</v>
-      </c>
-      <c r="J29" t="n">
-        <v>8</v>
-      </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="M29" t="n">
-        <v>15</v>
+        <v>6.08</v>
       </c>
       <c r="N29" t="n">
-        <v>37</v>
-      </c>
-      <c r="O29" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.66</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>59</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" t="n">
+        <v>21</v>
+      </c>
+      <c r="G30" t="n">
         <v>24</v>
       </c>
-      <c r="F30" t="n">
-        <v>13</v>
-      </c>
-      <c r="G30" t="n">
-        <v>13</v>
-      </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="M30" t="n">
-        <v>9</v>
+        <v>5.55</v>
       </c>
       <c r="N30" t="n">
-        <v>29</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>46</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G31" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I31" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" t="n">
         <v>14</v>
       </c>
-      <c r="J31" t="n">
-        <v>8</v>
-      </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N31" t="n">
-        <v>28</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C32" t="n">
+        <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E32" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n">
         <v>4</v>
       </c>
-      <c r="G32" t="n">
-        <v>37</v>
-      </c>
-      <c r="H32" t="n">
-        <v>14</v>
-      </c>
-      <c r="I32" t="n">
-        <v>33</v>
-      </c>
       <c r="J32" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L32" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>35</v>
+        <v>2.48</v>
       </c>
       <c r="N32" t="n">
-        <v>58</v>
-      </c>
-      <c r="O32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.55</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>43</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E33" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G33" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="L33" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="M33" t="n">
-        <v>25</v>
+        <v>7.66</v>
       </c>
       <c r="N33" t="n">
-        <v>51</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.76</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>32</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
         <v>16</v>
       </c>
-      <c r="H34" t="n">
-        <v>11</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10</v>
-      </c>
-      <c r="J34" t="n">
-        <v>12</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="M34" t="n">
-        <v>12</v>
+        <v>2.19</v>
       </c>
       <c r="N34" t="n">
-        <v>35</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C35" t="n">
+        <v>30</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>1.86</v>
       </c>
       <c r="N35" t="n">
-        <v>36</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0.98</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>33</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>37</v>
       </c>
       <c r="D36" t="n">
+        <v>16</v>
+      </c>
+      <c r="E36" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" t="n">
+        <v>12</v>
+      </c>
+      <c r="G36" t="n">
+        <v>15</v>
+      </c>
+      <c r="H36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
         <v>2</v>
       </c>
-      <c r="E36" t="n">
-        <v>34</v>
-      </c>
-      <c r="F36" t="n">
-        <v>6</v>
-      </c>
-      <c r="G36" t="n">
-        <v>22</v>
-      </c>
-      <c r="H36" t="n">
-        <v>8</v>
-      </c>
-      <c r="I36" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" t="n">
-        <v>15</v>
-      </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="L36" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="M36" t="n">
-        <v>15</v>
+        <v>3.57</v>
       </c>
       <c r="N36" t="n">
-        <v>37</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>33</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>17</v>
       </c>
       <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>9</v>
+      </c>
+      <c r="I37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="n">
-        <v>53</v>
-      </c>
-      <c r="F37" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" t="n">
-        <v>35</v>
-      </c>
-      <c r="H37" t="n">
-        <v>20</v>
-      </c>
-      <c r="I37" t="n">
-        <v>18</v>
-      </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>26</v>
+        <v>1.88</v>
       </c>
       <c r="N37" t="n">
-        <v>52</v>
-      </c>
-      <c r="O37" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.34</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5</v>
+      </c>
+      <c r="L38" t="n">
         <v>33</v>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="n">
-        <v>15</v>
-      </c>
-      <c r="F38" t="n">
-        <v>13</v>
-      </c>
-      <c r="G38" t="n">
-        <v>11</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4</v>
-      </c>
-      <c r="J38" t="n">
-        <v>6</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>3</v>
-      </c>
       <c r="M38" t="n">
-        <v>6</v>
+        <v>1.52</v>
       </c>
       <c r="N38" t="n">
-        <v>33</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.96</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>33</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>29</v>
       </c>
       <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>23</v>
+      </c>
+      <c r="F39" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="n">
-        <v>31</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="J39" t="n">
         <v>6</v>
       </c>
-      <c r="G39" t="n">
-        <v>16</v>
-      </c>
-      <c r="H39" t="n">
-        <v>7</v>
-      </c>
-      <c r="I39" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" t="n">
-        <v>9</v>
-      </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>15</v>
+        <v>2.34</v>
       </c>
       <c r="N39" t="n">
-        <v>42</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.24</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>33</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
+        <v>38</v>
+      </c>
+      <c r="F40" t="n">
+        <v>22</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" t="n">
+        <v>22</v>
+      </c>
+      <c r="I40" t="n">
+        <v>10</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" t="n">
         <v>32</v>
       </c>
-      <c r="F40" t="n">
-        <v>6</v>
-      </c>
-      <c r="G40" t="n">
-        <v>21</v>
-      </c>
-      <c r="H40" t="n">
-        <v>11</v>
-      </c>
-      <c r="I40" t="n">
-        <v>11</v>
-      </c>
-      <c r="J40" t="n">
-        <v>12</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
       <c r="L40" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="M40" t="n">
-        <v>13</v>
+        <v>7.22</v>
       </c>
       <c r="N40" t="n">
-        <v>56</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.59</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>33</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="N41" t="n">
-        <v>31</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.06</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>55</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E42" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>21</v>
+      </c>
+      <c r="H42" t="n">
+        <v>23</v>
+      </c>
+      <c r="I42" t="n">
         <v>5</v>
-      </c>
-      <c r="G42" t="n">
-        <v>13</v>
-      </c>
-      <c r="H42" t="n">
-        <v>11</v>
-      </c>
-      <c r="I42" t="n">
-        <v>26</v>
       </c>
       <c r="J42" t="n">
         <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="M42" t="n">
-        <v>18</v>
+        <v>6.58</v>
       </c>
       <c r="N42" t="n">
-        <v>46</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C43" t="n">
+        <v>48</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E43" t="n">
+        <v>30</v>
+      </c>
+      <c r="F43" t="n">
+        <v>23</v>
+      </c>
+      <c r="G43" t="n">
         <v>18</v>
       </c>
-      <c r="F43" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" t="n">
-        <v>6</v>
-      </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I43" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="M43" t="n">
-        <v>8</v>
+        <v>4.66</v>
       </c>
       <c r="N43" t="n">
-        <v>36</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>33</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C44" t="n">
+        <v>45</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" t="n">
         <v>18</v>
       </c>
-      <c r="F44" t="n">
-        <v>11</v>
-      </c>
       <c r="G44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>6.67</v>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>18</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I45" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="M45" t="n">
-        <v>18</v>
+        <v>1.12</v>
       </c>
       <c r="N45" t="n">
-        <v>32</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.59</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>44</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>70</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G46" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="M46" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="N46" t="n">
-        <v>37</v>
-      </c>
-      <c r="O46" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>44</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>52</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
+        <v>42</v>
+      </c>
+      <c r="F47" t="n">
         <v>17</v>
       </c>
-      <c r="F47" t="n">
-        <v>6</v>
-      </c>
       <c r="G47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
         <v>9</v>
       </c>
-      <c r="J47" t="n">
-        <v>7</v>
-      </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>6.03</v>
       </c>
       <c r="N47" t="n">
-        <v>33</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.66</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>49</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F48" t="n">
+        <v>13</v>
+      </c>
+      <c r="G48" t="n">
+        <v>22</v>
+      </c>
+      <c r="H48" t="n">
+        <v>26</v>
+      </c>
+      <c r="I48" t="n">
         <v>3</v>
       </c>
-      <c r="G48" t="n">
-        <v>23</v>
-      </c>
-      <c r="H48" t="n">
-        <v>7</v>
-      </c>
-      <c r="I48" t="n">
-        <v>6</v>
-      </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="M48" t="n">
-        <v>12</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>41</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Attacking</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>18</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="M49" t="n">
-        <v>16</v>
+        <v>1.71</v>
       </c>
       <c r="N49" t="n">
-        <v>42</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
@@ -3132,7 +2736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3191,434 +2795,403 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Assists</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>22.20833333333333</v>
+        <v>3.645833333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>12.98273539897183</v>
+        <v>2.928143579590153</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Assists</t>
+          <t>Attempts At Goal</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>3.645833333333333</v>
+        <v>41.95833333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>2.928143579590153</v>
+        <v>18.07661982775439</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>29.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>52.25</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Attempts At Goal</t>
+          <t>Attempts At Goal Conv. Rate (%)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>41.95833333333334</v>
+        <v>11.79166666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>18.07661982775439</v>
+        <v>6.129657007978586</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H4" t="n">
         <v>15</v>
       </c>
-      <c r="F4" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="G4" t="n">
-        <v>37</v>
-      </c>
-      <c r="H4" t="n">
-        <v>52.25</v>
-      </c>
       <c r="I4" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Attempts At Goal Conv. Rate (%)</t>
+          <t>Attempts Inside the Penalty Area</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>11.79166666666667</v>
+        <v>25.8125</v>
       </c>
       <c r="D5" t="n">
-        <v>6.129657007978587</v>
+        <v>13.33633055851412</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>15.75</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Attempts Inside the Penalty Area</t>
+          <t>Attempts On Target</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>25.8125</v>
+        <v>14.20833333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>13.33633055851412</v>
+        <v>7.491721199085207</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>15.75</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Attempts On Target</t>
+          <t>Attempts Outside the Penalty Area</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>14.22916666666667</v>
+        <v>16.14583333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>7.492519910546056</v>
+        <v>6.964926061018953</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="I7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Attempts Outside the Penalty Area</t>
+          <t>Corners</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>16.14583333333333</v>
+        <v>15.27083333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>6.964926061018953</v>
+        <v>7.911046904207266</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="H8" t="n">
-        <v>20.25</v>
+        <v>22</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Corners</t>
+          <t>Goals</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>15.27083333333333</v>
+        <v>5.020833333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>7.911046904207267</v>
+        <v>3.322967037013461</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" t="n">
-        <v>9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="H9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Goals</t>
+          <t>Headed Attempts at Goal</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>5.020833333333333</v>
+        <v>6.875</v>
       </c>
       <c r="D10" t="n">
-        <v>3.322967037013461</v>
+        <v>4.045617539584748</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Headed Attempts at Goal</t>
+          <t>Off-Target Attempts</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>6.875</v>
+        <v>17.79166666666667</v>
       </c>
       <c r="D11" t="n">
-        <v>4.045617539584748</v>
+        <v>7.573633809342394</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>13.75</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>23.5</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Off-Target Attempts</t>
+          <t>Possession Control (%)</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>17.79166666666667</v>
+        <v>45.20833333333334</v>
       </c>
       <c r="D12" t="n">
-        <v>7.573633809342394</v>
+        <v>8.939413882765241</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>13.75</v>
+        <v>37</v>
       </c>
       <c r="G12" t="n">
-        <v>15.5</v>
+        <v>45.5</v>
       </c>
       <c r="H12" t="n">
-        <v>23.5</v>
+        <v>52</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Possession Control (%)</t>
+          <t>xG</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>45.20833333333334</v>
+        <v>4.265833333333333</v>
       </c>
       <c r="D13" t="n">
-        <v>8.939413882765239</v>
+        <v>2.328106557235723</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>1.12</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>45.5</v>
+        <v>3.735</v>
       </c>
       <c r="H13" t="n">
-        <v>52</v>
+        <v>6.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>62</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xG</t>
+          <t>xG Efficiency</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>4.265833333333333</v>
+        <v>1.181458333333333</v>
       </c>
       <c r="D14" t="n">
-        <v>2.328106557235723</v>
+        <v>0.5353344136118685</v>
       </c>
       <c r="E14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>3.735</v>
+        <v>1.13</v>
       </c>
       <c r="H14" t="n">
-        <v>6.0425</v>
+        <v>1.525</v>
       </c>
       <c r="I14" t="n">
-        <v>8.640000000000001</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>xG Efficiency</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>48</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.181458333333333</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5353344136118685</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.525</v>
-      </c>
-      <c r="I15" t="n">
         <v>2.52</v>
       </c>
     </row>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Attacking.xlsx
@@ -665,19 +665,19 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
         <v>10</v>
@@ -686,19 +686,19 @@
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M5" t="n">
-        <v>3.63</v>
+        <v>3.86</v>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="6">
@@ -2364,43 +2364,43 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C42" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G42" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H42" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M42" t="n">
-        <v>6.58</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="43">
@@ -2745,8 +2745,8 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2802,10 +2802,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>3.645833333333333</v>
+        <v>3.708333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>2.928143579590153</v>
+        <v>2.967614797889457</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="I2" t="n">
         <v>12</v>
@@ -2833,16 +2833,16 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>41.95833333333334</v>
+        <v>42.54166666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>18.07661982775439</v>
+        <v>18.64330161305827</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>29.75</v>
+        <v>30.75</v>
       </c>
       <c r="G3" t="n">
         <v>37</v>
@@ -2864,10 +2864,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>11.79166666666667</v>
+        <v>11.72916666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>6.129657007978586</v>
+        <v>5.991978976660181</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>25.8125</v>
+        <v>26.20833333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>13.33633055851412</v>
+        <v>13.64591487983863</v>
       </c>
       <c r="E5" t="n">
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>15.75</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
         <v>22</v>
@@ -2926,10 +2926,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>14.20833333333333</v>
+        <v>14.41666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>7.491721199085207</v>
+        <v>7.679298874615687</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -2941,7 +2941,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="I6" t="n">
         <v>34</v>
@@ -2957,10 +2957,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>16.14583333333333</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>6.964926061018953</v>
+        <v>7.161758173929358</v>
       </c>
       <c r="E7" t="n">
         <v>4</v>
@@ -2988,10 +2988,10 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>15.27083333333333</v>
+        <v>15.45833333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>7.911046904207266</v>
+        <v>8.199528614715977</v>
       </c>
       <c r="E8" t="n">
         <v>5</v>
@@ -3019,10 +3019,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>5.020833333333333</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="D9" t="n">
-        <v>3.322967037013461</v>
+        <v>3.350664166193014</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3050,10 +3050,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>6.875</v>
+        <v>6.979166666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>4.045617539584748</v>
+        <v>4.123051871804265</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -3062,7 +3062,7 @@
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -3081,10 +3081,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>17.79166666666667</v>
+        <v>18.02083333333333</v>
       </c>
       <c r="D11" t="n">
-        <v>7.573633809342394</v>
+        <v>7.777462210754631</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
         <v>13.75</v>
       </c>
       <c r="G11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
         <v>23.5</v>
@@ -3112,10 +3112,10 @@
         <v>48</v>
       </c>
       <c r="C12" t="n">
-        <v>45.20833333333334</v>
+        <v>45.10416666666666</v>
       </c>
       <c r="D12" t="n">
-        <v>8.939413882765241</v>
+        <v>8.882781774688466</v>
       </c>
       <c r="E12" t="n">
         <v>28</v>
@@ -3130,7 +3130,7 @@
         <v>52</v>
       </c>
       <c r="I12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3143,10 +3143,10 @@
         <v>48</v>
       </c>
       <c r="C13" t="n">
-        <v>4.265833333333333</v>
+        <v>4.321874999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>2.328106557235723</v>
+        <v>2.404741465512966</v>
       </c>
       <c r="E13" t="n">
         <v>1.12</v>
@@ -3155,13 +3155,13 @@
         <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.735</v>
+        <v>3.81</v>
       </c>
       <c r="H13" t="n">
         <v>6.0425</v>
       </c>
       <c r="I13" t="n">
-        <v>8.640000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3174,22 +3174,22 @@
         <v>48</v>
       </c>
       <c r="C14" t="n">
-        <v>1.181458333333333</v>
+        <v>1.182291666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5353344136118685</v>
+        <v>0.5319664026478546</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="G14" t="n">
         <v>1.13</v>
       </c>
       <c r="H14" t="n">
-        <v>1.525</v>
+        <v>1.515</v>
       </c>
       <c r="I14" t="n">
         <v>2.52</v>
